--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_11_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_11_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76790.02591433519</v>
+        <v>79678.46129236606</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11084646.13170057</v>
+        <v>11084373.30616851</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21902852.37064991</v>
+        <v>21903018.1574896</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4111190.038794523</v>
+        <v>4111122.409036938</v>
       </c>
     </row>
     <row r="11">
@@ -7959,22 +7959,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>213.9533887334228</v>
+        <v>214.0546037115793</v>
       </c>
       <c r="L2" t="n">
-        <v>228.1535908493842</v>
+        <v>228.279156979828</v>
       </c>
       <c r="M2" t="n">
-        <v>221.875499558931</v>
+        <v>222.0152160730529</v>
       </c>
       <c r="N2" t="n">
-        <v>220.805264601616</v>
+        <v>220.9472418750055</v>
       </c>
       <c r="O2" t="n">
-        <v>221.9701109191742</v>
+        <v>222.1041760324344</v>
       </c>
       <c r="P2" t="n">
-        <v>224.2958500266263</v>
+        <v>224.4102714990879</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8035,28 +8035,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J3" t="n">
-        <v>124.3990228930818</v>
+        <v>124.4392452907996</v>
       </c>
       <c r="K3" t="n">
-        <v>133.673476710208</v>
+        <v>133.7422231944371</v>
       </c>
       <c r="L3" t="n">
-        <v>132.9500401572327</v>
+        <v>133.0424782891217</v>
       </c>
       <c r="M3" t="n">
-        <v>135.5940339220183</v>
+        <v>135.7019048619078</v>
       </c>
       <c r="N3" t="n">
-        <v>124.6286177437107</v>
+        <v>124.739343706399</v>
       </c>
       <c r="O3" t="n">
-        <v>136.4550746331237</v>
+        <v>136.5563672569108</v>
       </c>
       <c r="P3" t="n">
-        <v>129.045577225651</v>
+        <v>129.1268734863556</v>
       </c>
       <c r="Q3" t="n">
-        <v>136.6869816331913</v>
+        <v>136.741326030535</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8120,16 +8120,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L4" t="n">
-        <v>131.6674959533694</v>
+        <v>131.7205602141892</v>
       </c>
       <c r="M4" t="n">
-        <v>135.5337183738346</v>
+        <v>135.5896671967106</v>
       </c>
       <c r="N4" t="n">
-        <v>124.3741346291676</v>
+        <v>124.4287531140874</v>
       </c>
       <c r="O4" t="n">
-        <v>135.3979155010231</v>
+        <v>135.4483645121045</v>
       </c>
       <c r="P4" t="n">
         <v>135.0065633140411</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>101.2048693508069</v>
+        <v>100.9387195582597</v>
       </c>
       <c r="K5" t="n">
-        <v>100.4288359696037</v>
+        <v>100.0299464227919</v>
       </c>
       <c r="L5" t="n">
-        <v>87.31634461822844</v>
+        <v>86.82148686318186</v>
       </c>
       <c r="M5" t="n">
-        <v>65.16692669460943</v>
+        <v>64.61630209323863</v>
       </c>
       <c r="N5" t="n">
-        <v>61.56098319458087</v>
+        <v>61.00144891149961</v>
       </c>
       <c r="O5" t="n">
-        <v>71.60025162269176</v>
+        <v>71.0718992657024</v>
       </c>
       <c r="P5" t="n">
-        <v>95.95865404672682</v>
+        <v>95.50771753390021</v>
       </c>
       <c r="Q5" t="n">
-        <v>120.7202928895249</v>
+        <v>120.3816583481039</v>
       </c>
       <c r="R5" t="n">
         <v>65.71641987298243</v>
@@ -8272,28 +8272,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J6" t="n">
-        <v>79.28485308176103</v>
+        <v>79.12633608862856</v>
       </c>
       <c r="K6" t="n">
-        <v>56.56617482341558</v>
+        <v>56.29524403393702</v>
       </c>
       <c r="L6" t="n">
-        <v>29.26975713836474</v>
+        <v>28.90545725697471</v>
       </c>
       <c r="M6" t="n">
-        <v>14.60403392201833</v>
+        <v>14.17891314335149</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4363724606917856</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22.84343312368972</v>
+        <v>22.44423757443683</v>
       </c>
       <c r="P6" t="n">
-        <v>37.86221873508495</v>
+        <v>37.54182911310821</v>
       </c>
       <c r="Q6" t="n">
-        <v>75.73332125583282</v>
+        <v>75.51914927829571</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8354,22 +8354,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K7" t="n">
-        <v>79.98834013774851</v>
+        <v>79.82491575659759</v>
       </c>
       <c r="L7" t="n">
-        <v>72.14965988779565</v>
+        <v>71.94053294496764</v>
       </c>
       <c r="M7" t="n">
-        <v>72.78050525908047</v>
+        <v>72.56001021962938</v>
       </c>
       <c r="N7" t="n">
-        <v>63.11305266195446</v>
+        <v>62.89780050171086</v>
       </c>
       <c r="O7" t="n">
-        <v>78.81339091085917</v>
+        <v>78.61457070130248</v>
       </c>
       <c r="P7" t="n">
-        <v>86.69298765570502</v>
+        <v>86.52286261917671</v>
       </c>
       <c r="Q7" t="n">
         <v>65.34295837775146</v>
@@ -8430,28 +8430,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>92.33364322015366</v>
+        <v>92.06191329280011</v>
       </c>
       <c r="K8" t="n">
-        <v>87.1331676278952</v>
+        <v>86.72591490550931</v>
       </c>
       <c r="L8" t="n">
-        <v>70.82189235692201</v>
+        <v>70.31665934305323</v>
       </c>
       <c r="M8" t="n">
-        <v>46.81367041320252</v>
+        <v>46.25150133729363</v>
       </c>
       <c r="N8" t="n">
-        <v>42.91075203880209</v>
+        <v>42.33948647951536</v>
       </c>
       <c r="O8" t="n">
-        <v>53.98936720058131</v>
+        <v>53.44993733213093</v>
       </c>
       <c r="P8" t="n">
-        <v>80.92817163466663</v>
+        <v>80.46778072209531</v>
       </c>
       <c r="Q8" t="n">
-        <v>109.4330265578667</v>
+        <v>109.0872921559756</v>
       </c>
       <c r="R8" t="n">
         <v>65.71641987298243</v>
@@ -8509,28 +8509,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J9" t="n">
-        <v>74.00121157232709</v>
+        <v>73.83937108913167</v>
       </c>
       <c r="K9" t="n">
-        <v>47.53558991775527</v>
+        <v>47.25897875440141</v>
       </c>
       <c r="L9" t="n">
-        <v>17.1270212893082</v>
+        <v>16.75508344424118</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4340339220184433</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>9.53756519916152</v>
+        <v>9.130000058643361</v>
       </c>
       <c r="P9" t="n">
-        <v>27.18308665961332</v>
+        <v>26.85597970277001</v>
       </c>
       <c r="Q9" t="n">
-        <v>68.5946042747008</v>
+        <v>68.37594193669796</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8591,22 +8591,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K10" t="n">
-        <v>74.54112702299446</v>
+        <v>74.37427626277801</v>
       </c>
       <c r="L10" t="n">
-        <v>65.17910251074652</v>
+        <v>64.96559098237566</v>
       </c>
       <c r="M10" t="n">
-        <v>65.43102984924447</v>
+        <v>65.20591187910269</v>
       </c>
       <c r="N10" t="n">
-        <v>55.9383313504791</v>
+        <v>55.71856618250388</v>
       </c>
       <c r="O10" t="n">
-        <v>72.18637451741658</v>
+        <v>71.98338581476828</v>
       </c>
       <c r="P10" t="n">
-        <v>81.02243027865588</v>
+        <v>80.84873837615825</v>
       </c>
       <c r="Q10" t="n">
         <v>65.34295837775146</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K11" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L11" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M11" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.630878662203785e-12</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P11" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q11" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,10 +8746,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K12" t="n">
-        <v>26.69577859700047</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -8764,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q12" t="n">
-        <v>52.12064201054979</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L13" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M13" t="n">
-        <v>48.47070198039194</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N13" t="n">
-        <v>39.38128217015115</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O13" t="n">
-        <v>56.89325976331816</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P13" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K14" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L14" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M14" t="n">
-        <v>4.460002071493847</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>13.34886468801838</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P14" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q14" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,10 +8983,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K15" t="n">
-        <v>26.69577859700047</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q15" t="n">
-        <v>52.12064201054979</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L16" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M16" t="n">
-        <v>48.47070198039194</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N16" t="n">
-        <v>39.38128217015115</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O16" t="n">
-        <v>56.89325976331816</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P16" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K17" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L17" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M17" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P17" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q17" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,10 +9220,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K18" t="n">
-        <v>26.69577859700047</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -9238,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q18" t="n">
-        <v>52.12064201054979</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L19" t="n">
-        <v>49.09320087140219</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M19" t="n">
-        <v>48.47070198039194</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N19" t="n">
-        <v>39.38128217015115</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O19" t="n">
-        <v>56.89325976331816</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P19" t="n">
-        <v>67.93652863931159</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K20" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L20" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M20" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P20" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q20" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,10 +9457,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K21" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -9475,10 +9475,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q21" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L22" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M22" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N22" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O22" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P22" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K23" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L23" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M23" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P23" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q23" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,10 +9694,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K24" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -9712,10 +9712,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q24" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L25" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M25" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N25" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O25" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P25" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K26" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L26" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M26" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P26" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q26" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,10 +9931,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K27" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -9949,10 +9949,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q27" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L28" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M28" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N28" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O28" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P28" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K29" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L29" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M29" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P29" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q29" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,10 +10168,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K30" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -10186,10 +10186,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L31" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M31" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N31" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O31" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P31" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679383</v>
       </c>
       <c r="K32" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916996</v>
       </c>
       <c r="L32" t="n">
-        <v>32.75777175390681</v>
+        <v>32.8711910981084</v>
       </c>
       <c r="M32" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601003</v>
       </c>
       <c r="P32" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917247</v>
       </c>
       <c r="Q32" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126157</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,10 +10405,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K33" t="n">
-        <v>26.69577859700048</v>
+        <v>26.75787480980772</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -10423,10 +10423,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219109</v>
       </c>
       <c r="Q33" t="n">
-        <v>52.1206420105498</v>
+        <v>52.16972933916271</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979796</v>
       </c>
       <c r="L34" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899257</v>
       </c>
       <c r="M34" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856002</v>
       </c>
       <c r="N34" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215854</v>
       </c>
       <c r="O34" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P34" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K35" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L35" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M35" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P35" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q35" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,10 +10642,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K36" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -10660,10 +10660,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q36" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L37" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M37" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N37" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O37" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P37" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K38" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L38" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M38" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P38" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q38" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,10 +10879,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K39" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10897,10 +10897,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q39" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L40" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M40" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N40" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O40" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P40" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K41" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L41" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M41" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P41" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q41" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,10 +11116,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K42" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11134,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q42" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L43" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M43" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N43" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O43" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P43" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>71.86158291864606</v>
+        <v>71.92258334679381</v>
       </c>
       <c r="K44" t="n">
-        <v>56.45085607010614</v>
+        <v>56.54227989916993</v>
       </c>
       <c r="L44" t="n">
-        <v>32.75777175390681</v>
+        <v>32.87119109810837</v>
       </c>
       <c r="M44" t="n">
-        <v>4.460002071493818</v>
+        <v>4.586202945486093</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>13.34886468801835</v>
+        <v>13.46996085601</v>
       </c>
       <c r="P44" t="n">
-        <v>46.24244299145042</v>
+        <v>46.34579576917244</v>
       </c>
       <c r="Q44" t="n">
-        <v>83.38548886942436</v>
+        <v>83.46310250126155</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,10 +11353,10 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>61.80819270440253</v>
+        <v>61.84452414151257</v>
       </c>
       <c r="K45" t="n">
-        <v>26.69577859700048</v>
+        <v>26.7578748098077</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -11371,10 +11371,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.538935716217026</v>
+        <v>2.612367688219081</v>
       </c>
       <c r="Q45" t="n">
-        <v>52.1206420105498</v>
+        <v>52.1697293391627</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>61.97063521971573</v>
+        <v>62.00809140979794</v>
       </c>
       <c r="L46" t="n">
-        <v>49.09320087140222</v>
+        <v>49.14113189899255</v>
       </c>
       <c r="M46" t="n">
-        <v>48.47070198039196</v>
+        <v>48.52123852856</v>
       </c>
       <c r="N46" t="n">
-        <v>39.38128217015117</v>
+        <v>39.43061707215853</v>
       </c>
       <c r="O46" t="n">
-        <v>56.89325976331817</v>
+        <v>56.93882853040725</v>
       </c>
       <c r="P46" t="n">
-        <v>67.93652863931158</v>
+        <v>67.97552059180406</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22519,16 +22519,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G2" t="n">
-        <v>415.2544963091049</v>
+        <v>415.2552920008841</v>
       </c>
       <c r="H2" t="n">
-        <v>338.9807518645109</v>
+        <v>338.9889007429445</v>
       </c>
       <c r="I2" t="n">
-        <v>208.6160704749285</v>
+        <v>208.6467463822456</v>
       </c>
       <c r="J2" t="n">
-        <v>7.854877294310995</v>
+        <v>7.922410639454649</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -22549,19 +22549,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.781191676856366</v>
+        <v>4.867117437475873</v>
       </c>
       <c r="R2" t="n">
-        <v>146.8387862828582</v>
+        <v>146.8887686565825</v>
       </c>
       <c r="S2" t="n">
-        <v>207.9207731038333</v>
+        <v>207.9389049302515</v>
       </c>
       <c r="T2" t="n">
-        <v>222.8846736847344</v>
+        <v>222.8881568254978</v>
       </c>
       <c r="U2" t="n">
-        <v>251.3417936113541</v>
+        <v>251.3418572666964</v>
       </c>
       <c r="V2" t="n">
         <v>327.7522584701349</v>
@@ -22598,13 +22598,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3177058424559</v>
+        <v>137.3181315750904</v>
       </c>
       <c r="H3" t="n">
-        <v>111.9861612176285</v>
+        <v>111.9902728985985</v>
       </c>
       <c r="I3" t="n">
-        <v>88.50795360613206</v>
+        <v>88.5226115060478</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -22631,16 +22631,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>98.55526811490729</v>
+        <v>98.58170088321393</v>
       </c>
       <c r="S3" t="n">
-        <v>171.2037371415737</v>
+        <v>171.2116449385346</v>
       </c>
       <c r="T3" t="n">
-        <v>200.0606909589725</v>
+        <v>200.0624069602493</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9396839677673</v>
+        <v>225.9397119764932</v>
       </c>
       <c r="V3" t="n">
         <v>232.8005871494253</v>
@@ -22677,19 +22677,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
-        <v>167.9693400141965</v>
+        <v>167.9696969341359</v>
       </c>
       <c r="H4" t="n">
-        <v>162.0347790648166</v>
+        <v>162.0379524075512</v>
       </c>
       <c r="I4" t="n">
-        <v>154.7997208288976</v>
+        <v>154.8104543848956</v>
       </c>
       <c r="J4" t="n">
-        <v>91.82927847732853</v>
+        <v>91.85451271704937</v>
       </c>
       <c r="K4" t="n">
-        <v>19.75539346522712</v>
+        <v>19.79686107274064</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22704,22 +22704,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1042604072376605</v>
+        <v>0.1474282515537739</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.35004325169437</v>
+        <v>84.37993042953531</v>
       </c>
       <c r="R4" t="n">
-        <v>176.3204077706121</v>
+        <v>176.3364561889816</v>
       </c>
       <c r="S4" t="n">
-        <v>223.6394832828739</v>
+        <v>223.6457034240009</v>
       </c>
       <c r="T4" t="n">
-        <v>227.8531304118881</v>
+        <v>227.8546554334476</v>
       </c>
       <c r="U4" t="n">
-        <v>286.317849028622</v>
+        <v>286.3178684969824</v>
       </c>
       <c r="V4" t="n">
         <v>252.137643323828</v>
@@ -22756,13 +22756,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>414.3620339975471</v>
+        <v>414.3588981658848</v>
       </c>
       <c r="H5" t="n">
-        <v>329.8408222162697</v>
+        <v>329.8087073802583</v>
       </c>
       <c r="I5" t="n">
-        <v>174.2094172085968</v>
+        <v>174.0885230584365</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22789,16 +22789,16 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>90.77765060446627</v>
+        <v>90.58066941881005</v>
       </c>
       <c r="S5" t="n">
-        <v>187.5837881792102</v>
+        <v>187.5123304152058</v>
       </c>
       <c r="T5" t="n">
-        <v>218.9779199158901</v>
+        <v>218.9641928127885</v>
       </c>
       <c r="U5" t="n">
-        <v>251.2703966264295</v>
+        <v>251.2701457598965</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -22835,13 +22835,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>136.8401964084937</v>
+        <v>136.8385185906377</v>
       </c>
       <c r="H6" t="n">
-        <v>107.3744253685719</v>
+        <v>107.3582211803319</v>
       </c>
       <c r="I6" t="n">
-        <v>72.0673875683962</v>
+        <v>72.00962059397116</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -22868,16 +22868,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>68.90779641679406</v>
+        <v>68.80362453272261</v>
       </c>
       <c r="S6" t="n">
-        <v>162.3342088396869</v>
+        <v>162.3030441088983</v>
       </c>
       <c r="T6" t="n">
-        <v>198.135992845765</v>
+        <v>198.1292300623896</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9082688734277</v>
+        <v>225.908158490674</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -22914,16 +22914,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.569012145344</v>
+        <v>167.5676055192152</v>
       </c>
       <c r="H7" t="n">
-        <v>158.475500376292</v>
+        <v>158.4629941912556</v>
       </c>
       <c r="I7" t="n">
-        <v>142.7607700092255</v>
+        <v>142.7184689252781</v>
       </c>
       <c r="J7" t="n">
-        <v>63.52609814945966</v>
+        <v>63.42664968215054</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22944,19 +22944,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>50.82804325169438</v>
+        <v>50.71025749466926</v>
       </c>
       <c r="R7" t="n">
-        <v>158.3202110493006</v>
+        <v>158.2569640235438</v>
       </c>
       <c r="S7" t="n">
-        <v>216.6628603320542</v>
+        <v>216.6383466748816</v>
       </c>
       <c r="T7" t="n">
-        <v>226.1426386086094</v>
+        <v>226.1366284787861</v>
       </c>
       <c r="U7" t="n">
-        <v>286.2960129630483</v>
+        <v>286.2959362379867</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -22993,13 +22993,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>414.2575113844818</v>
+        <v>414.2543098065221</v>
       </c>
       <c r="H8" t="n">
-        <v>328.7703800052144</v>
+        <v>328.737591844935</v>
       </c>
       <c r="I8" t="n">
-        <v>170.1798091683959</v>
+        <v>170.0563803341062</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23026,16 +23026,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>84.21193201150147</v>
+        <v>84.01082088999308</v>
       </c>
       <c r="S8" t="n">
-        <v>185.201979133984</v>
+        <v>185.1290231762283</v>
       </c>
       <c r="T8" t="n">
-        <v>218.5203721771967</v>
+        <v>218.5063572696783</v>
       </c>
       <c r="U8" t="n">
-        <v>251.2620348173842</v>
+        <v>251.2617786911475</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,13 +23072,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>136.7842718801918</v>
+        <v>136.7825588849655</v>
       </c>
       <c r="H9" t="n">
-        <v>106.8343121610248</v>
+        <v>106.817768233445</v>
       </c>
       <c r="I9" t="n">
-        <v>70.141915870283</v>
+        <v>70.08293774516886</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>65.43557000169974</v>
+        <v>65.32921403493339</v>
       </c>
       <c r="S9" t="n">
-        <v>161.2954352547812</v>
+        <v>161.2636171197674</v>
       </c>
       <c r="T9" t="n">
-        <v>197.9105777514254</v>
+        <v>197.9036731785617</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9045896281446</v>
+        <v>225.9044769310903</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,16 +23151,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.5221268994424</v>
+        <v>167.5206907817879</v>
       </c>
       <c r="H10" t="n">
-        <v>158.0586479172756</v>
+        <v>158.0458795257661</v>
       </c>
       <c r="I10" t="n">
-        <v>141.3508027961107</v>
+        <v>141.3076148215571</v>
       </c>
       <c r="J10" t="n">
-        <v>60.21131126421378</v>
+        <v>60.10977774604451</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23181,19 +23181,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>46.90204325169441</v>
+        <v>46.78178798155719</v>
       </c>
       <c r="R10" t="n">
-        <v>156.2120799017597</v>
+        <v>156.1475068297698</v>
       </c>
       <c r="S10" t="n">
-        <v>215.8457783648411</v>
+        <v>215.8207507508087</v>
       </c>
       <c r="T10" t="n">
-        <v>225.9423107397569</v>
+        <v>225.9361746006879</v>
       </c>
       <c r="U10" t="n">
-        <v>286.2934555859991</v>
+        <v>286.2933772523089</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H11" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I11" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S11" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T11" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H12" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I12" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S12" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T12" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U12" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H13" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I13" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J13" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R13" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S13" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T13" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U13" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H14" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I14" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S14" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T14" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H15" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I15" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S15" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T15" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U15" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H16" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I16" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J16" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R16" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S16" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T16" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U16" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H17" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I17" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S17" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T17" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H18" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I18" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S18" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T18" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U18" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H19" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I19" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J19" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R19" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S19" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T19" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U19" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H20" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I20" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S20" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T20" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H21" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I21" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S21" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T21" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U21" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H22" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I22" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J22" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R22" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S22" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T22" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U22" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H23" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I23" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S23" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T23" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H24" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I24" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S24" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T24" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U24" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H25" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I25" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J25" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R25" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S25" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T25" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U25" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H26" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I26" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S26" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T26" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H27" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I27" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S27" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T27" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U27" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H28" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I28" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J28" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R28" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S28" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T28" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U28" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H29" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I29" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S29" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T29" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H30" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I30" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S30" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T30" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U30" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H31" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I31" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J31" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R31" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S31" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T31" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U31" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H32" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I32" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S32" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T32" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H33" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I33" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S33" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T33" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U33" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H34" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I34" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J34" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848996</v>
       </c>
       <c r="R34" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S34" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T34" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U34" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H35" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I35" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S35" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T35" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H36" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I36" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S36" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T36" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U36" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H37" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I37" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J37" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R37" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S37" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T37" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U37" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H38" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I38" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S38" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T38" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H39" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I39" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S39" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T39" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U39" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H40" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I40" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J40" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R40" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S40" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T40" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U40" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H41" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I41" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S41" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T41" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H42" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I42" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S42" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T42" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U42" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H43" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I43" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J43" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R43" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S43" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T43" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U43" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.0163053543311</v>
+        <v>414.0170240739369</v>
       </c>
       <c r="H44" t="n">
-        <v>326.300128748933</v>
+        <v>326.3074893360965</v>
       </c>
       <c r="I44" t="n">
-        <v>160.8807136910089</v>
+        <v>160.9084221286138</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>69.06027372004415</v>
+        <v>69.10542099048567</v>
       </c>
       <c r="S44" t="n">
-        <v>179.7054967219237</v>
+        <v>179.7218745449422</v>
       </c>
       <c r="T44" t="n">
-        <v>217.4644927802118</v>
+        <v>217.4676389752864</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2427383349722</v>
+        <v>251.2427958325407</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.6552152764182</v>
+        <v>136.6555998253092</v>
       </c>
       <c r="H45" t="n">
-        <v>105.5878970666851</v>
+        <v>105.5916109993956</v>
       </c>
       <c r="I45" t="n">
-        <v>65.6985196438679</v>
+        <v>65.71175959472041</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>57.42273981302047</v>
+        <v>57.4466155766215</v>
       </c>
       <c r="S45" t="n">
-        <v>158.8982654434605</v>
+        <v>158.905408270449</v>
       </c>
       <c r="T45" t="n">
-        <v>197.3903890721801</v>
+        <v>197.3919390740697</v>
       </c>
       <c r="U45" t="n">
-        <v>225.8960990621069</v>
+        <v>225.8961243613761</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.4139301781309</v>
+        <v>167.4142525710033</v>
       </c>
       <c r="H46" t="n">
-        <v>157.0966807041609</v>
+        <v>157.0995470698808</v>
       </c>
       <c r="I46" t="n">
-        <v>138.0970323043074</v>
+        <v>138.1067275372333</v>
       </c>
       <c r="J46" t="n">
-        <v>52.56180306749246</v>
+        <v>52.58459624356987</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>37.84204325169438</v>
+        <v>37.86903925848995</v>
       </c>
       <c r="R46" t="n">
-        <v>151.3471618689728</v>
+        <v>151.3616578248528</v>
       </c>
       <c r="S46" t="n">
-        <v>213.9602045943493</v>
+        <v>213.9658230228616</v>
       </c>
       <c r="T46" t="n">
-        <v>225.4800156577897</v>
+        <v>225.481393154608</v>
       </c>
       <c r="U46" t="n">
-        <v>286.2875539466548</v>
+        <v>286.2875715317206</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>366416.1896185669</v>
+        <v>366402.3808763221</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>357259.8042094142</v>
+        <v>357218.7764100882</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>356056.7847796371</v>
+        <v>356020.0915663616</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>354045.210395325</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>354045.2103953251</v>
+        <v>354047.4639007233</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70435.61416227664</v>
+        <v>70426.61646346406</v>
       </c>
       <c r="C2" t="n">
-        <v>75816.14361168401</v>
+        <v>75833.3562036838</v>
       </c>
       <c r="D2" t="n">
-        <v>76389.86863496268</v>
+        <v>76407.44210864045</v>
       </c>
       <c r="E2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324534</v>
       </c>
       <c r="F2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324537</v>
       </c>
       <c r="G2" t="n">
-        <v>77713.84945791353</v>
+        <v>77709.90440324534</v>
       </c>
       <c r="H2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324537</v>
       </c>
       <c r="I2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324537</v>
       </c>
       <c r="J2" t="n">
-        <v>77713.8494579135</v>
+        <v>77709.90440324537</v>
       </c>
       <c r="K2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324535</v>
       </c>
       <c r="L2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324534</v>
       </c>
       <c r="M2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324535</v>
       </c>
       <c r="N2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324535</v>
       </c>
       <c r="O2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324535</v>
       </c>
       <c r="P2" t="n">
-        <v>77713.84945791351</v>
+        <v>77709.90440324534</v>
       </c>
     </row>
     <row r="3">
@@ -26313,16 +26313,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11563.356</v>
+        <v>11372.62968807397</v>
       </c>
       <c r="C3" t="n">
-        <v>202153.644</v>
+        <v>203044.1822108271</v>
       </c>
       <c r="D3" t="n">
-        <v>22266.76399999996</v>
+        <v>22280.77012981693</v>
       </c>
       <c r="E3" t="n">
-        <v>48204.18000000012</v>
+        <v>47420.72226727416</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57583.11213781542</v>
+        <v>56649.73638563651</v>
       </c>
       <c r="C4" t="n">
-        <v>24835.17452741483</v>
+        <v>24307.18196373188</v>
       </c>
       <c r="D4" t="n">
-        <v>21116.59153403139</v>
+        <v>20653.20901911422</v>
       </c>
       <c r="E4" t="n">
-        <v>13299.87046447303</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="F4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="G4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="H4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="I4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="J4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="K4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="L4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="M4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="N4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="O4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
       <c r="P4" t="n">
-        <v>13299.87046447308</v>
+        <v>13097.69183178116</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33889.2</v>
+        <v>33884.88516240442</v>
       </c>
       <c r="C5" t="n">
-        <v>38728.8</v>
+        <v>38745.80483114667</v>
       </c>
       <c r="D5" t="n">
-        <v>39295.59999999999</v>
+        <v>39312.96135688073</v>
       </c>
       <c r="E5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="F5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="G5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="H5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="I5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="J5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="K5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="L5" t="n">
-        <v>6976</v>
+        <v>6972.102563257328</v>
       </c>
       <c r="M5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="N5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="O5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
       <c r="P5" t="n">
-        <v>6976</v>
+        <v>6972.10256325733</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-32600.05397553877</v>
+        <v>-31480.63477265084</v>
       </c>
       <c r="C6" t="n">
-        <v>-189901.4749157308</v>
+        <v>-190263.8128020219</v>
       </c>
       <c r="D6" t="n">
-        <v>-6289.086899068658</v>
+        <v>-5839.498397171432</v>
       </c>
       <c r="E6" t="n">
-        <v>9233.798993440358</v>
+        <v>10219.38774093269</v>
       </c>
       <c r="F6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820688</v>
       </c>
       <c r="G6" t="n">
-        <v>57437.97899344045</v>
+        <v>57640.11000820685</v>
       </c>
       <c r="H6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820688</v>
       </c>
       <c r="I6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820688</v>
       </c>
       <c r="J6" t="n">
-        <v>57437.97899344043</v>
+        <v>57640.11000820688</v>
       </c>
       <c r="K6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820687</v>
       </c>
       <c r="L6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820684</v>
       </c>
       <c r="M6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820687</v>
       </c>
       <c r="N6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820687</v>
       </c>
       <c r="O6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820687</v>
       </c>
       <c r="P6" t="n">
-        <v>57437.97899344044</v>
+        <v>57640.11000820685</v>
       </c>
     </row>
   </sheetData>
@@ -26675,49 +26675,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11.80207166992762</v>
       </c>
       <c r="C3" t="n">
-        <v>234</v>
+        <v>234.7800381259942</v>
       </c>
       <c r="D3" t="n">
-        <v>259.9999999999998</v>
+        <v>260.7963925174648</v>
       </c>
       <c r="E3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="F3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="G3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="H3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="I3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="L3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="M3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="N3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="O3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
       <c r="P3" t="n">
-        <v>320</v>
+        <v>319.8212184980426</v>
       </c>
     </row>
     <row r="4">
@@ -26892,16 +26892,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11.80207166992762</v>
       </c>
       <c r="C3" t="n">
-        <v>222</v>
+        <v>222.9779664560666</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>26.01635439147063</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>59.02482598057782</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -30959,49 +30959,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04824120603015071</v>
+        <v>0.04744551425096528</v>
       </c>
       <c r="H2" t="n">
-        <v>0.494050251256281</v>
+        <v>0.4859013728226984</v>
       </c>
       <c r="I2" t="n">
-        <v>1.859819095477387</v>
+        <v>1.829143188160341</v>
       </c>
       <c r="J2" t="n">
-        <v>4.094412060301508</v>
+        <v>4.026878715157869</v>
       </c>
       <c r="K2" t="n">
-        <v>6.13646231155779</v>
+        <v>6.03524733340123</v>
       </c>
       <c r="L2" t="n">
-        <v>7.612824120603015</v>
+        <v>7.487257990159211</v>
       </c>
       <c r="M2" t="n">
-        <v>8.470733668341708</v>
+        <v>8.331017154219815</v>
       </c>
       <c r="N2" t="n">
-        <v>8.607798994974875</v>
+        <v>8.465821721585371</v>
       </c>
       <c r="O2" t="n">
-        <v>8.128100502512563</v>
+        <v>7.994035389252334</v>
       </c>
       <c r="P2" t="n">
-        <v>6.937145728643216</v>
+        <v>6.822724256181627</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.209507537688443</v>
+        <v>5.123581777068932</v>
       </c>
       <c r="R2" t="n">
-        <v>3.030331658291457</v>
+        <v>2.980349284567201</v>
       </c>
       <c r="S2" t="n">
-        <v>1.099296482412061</v>
+        <v>1.081164655993873</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2111758793969848</v>
+        <v>0.2076927386336007</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003859296482412056</v>
+        <v>0.003795641140077222</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31038,49 +31038,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02581132075471698</v>
+        <v>0.02538558812022168</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2492830188679245</v>
+        <v>0.2451713378979305</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8886792452830189</v>
+        <v>0.8740213453672817</v>
       </c>
       <c r="J3" t="n">
-        <v>2.438603773584906</v>
+        <v>2.398381375867085</v>
       </c>
       <c r="K3" t="n">
-        <v>4.167962264150944</v>
+        <v>4.099215779921938</v>
       </c>
       <c r="L3" t="n">
-        <v>5.60433962264151</v>
+        <v>5.511901490752519</v>
       </c>
       <c r="M3" t="n">
-        <v>6.54</v>
+        <v>6.432129060110555</v>
       </c>
       <c r="N3" t="n">
-        <v>6.713094339622643</v>
+        <v>6.602368376934323</v>
       </c>
       <c r="O3" t="n">
-        <v>6.141169811320756</v>
+        <v>6.039877187533621</v>
       </c>
       <c r="P3" t="n">
-        <v>4.928830188679246</v>
+        <v>4.847533927974613</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.294792452830189</v>
+        <v>3.240448055486544</v>
       </c>
       <c r="R3" t="n">
-        <v>1.602566037735849</v>
+        <v>1.576133269429203</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4794339622641505</v>
+        <v>0.4715261653032402</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1040377358490566</v>
+        <v>0.102321734572297</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001698113207547171</v>
+        <v>0.001670104481593532</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31117,49 +31117,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02163934426229508</v>
+        <v>0.0212824243228203</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1923934426229509</v>
+        <v>0.1892200998883479</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6507540983606558</v>
+        <v>0.6400205423626326</v>
       </c>
       <c r="J4" t="n">
-        <v>1.529901639344262</v>
+        <v>1.504667399623395</v>
       </c>
       <c r="K4" t="n">
-        <v>2.514098360655737</v>
+        <v>2.472630753142213</v>
       </c>
       <c r="L4" t="n">
-        <v>3.217180327868852</v>
+        <v>3.164116067049121</v>
       </c>
       <c r="M4" t="n">
-        <v>3.392065573770491</v>
+        <v>3.336116750894459</v>
       </c>
       <c r="N4" t="n">
-        <v>3.311409836065576</v>
+        <v>3.256791351145767</v>
       </c>
       <c r="O4" t="n">
-        <v>3.058622950819673</v>
+        <v>3.008173939738275</v>
       </c>
       <c r="P4" t="n">
-        <v>2.617180327868851</v>
+        <v>2.574012483552738</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.812</v>
+        <v>1.782112822159071</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9729836065573767</v>
+        <v>0.9569351881879018</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3771147540983604</v>
+        <v>0.3708946129713319</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09245901639344258</v>
+        <v>0.09093399483386855</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00118032786885246</v>
+        <v>0.001160859508517472</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9407035175879388</v>
+        <v>0.9438393492502272</v>
       </c>
       <c r="H5" t="n">
-        <v>9.633979899497483</v>
+        <v>9.666094735508892</v>
       </c>
       <c r="I5" t="n">
-        <v>36.26647236180905</v>
+        <v>36.38736651196942</v>
       </c>
       <c r="J5" t="n">
-        <v>79.84103517587941</v>
+        <v>80.10718496842655</v>
       </c>
       <c r="K5" t="n">
-        <v>119.6610150753769</v>
+        <v>120.0599046221887</v>
       </c>
       <c r="L5" t="n">
-        <v>148.4500703517588</v>
+        <v>148.9449281068054</v>
       </c>
       <c r="M5" t="n">
-        <v>165.1793065326633</v>
+        <v>165.7299311340341</v>
       </c>
       <c r="N5" t="n">
-        <v>167.85208040201</v>
+        <v>168.4116146850913</v>
       </c>
       <c r="O5" t="n">
-        <v>158.497959798995</v>
+        <v>159.0263121559843</v>
       </c>
       <c r="P5" t="n">
-        <v>135.2743417085427</v>
+        <v>135.7252782213693</v>
       </c>
       <c r="Q5" t="n">
-        <v>101.5853969849246</v>
+        <v>101.9240315263455</v>
       </c>
       <c r="R5" t="n">
-        <v>59.09146733668342</v>
+        <v>59.28844852233964</v>
       </c>
       <c r="S5" t="n">
-        <v>21.43628140703519</v>
+        <v>21.50773917103957</v>
       </c>
       <c r="T5" t="n">
-        <v>4.117929648241205</v>
+        <v>4.131656751342871</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07525628140703508</v>
+        <v>0.07550714794001816</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,49 +31275,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.503320754716981</v>
+        <v>0.5049985725728932</v>
       </c>
       <c r="H6" t="n">
-        <v>4.861018867924529</v>
+        <v>4.877223056164522</v>
       </c>
       <c r="I6" t="n">
-        <v>17.32924528301887</v>
+        <v>17.38701225744391</v>
       </c>
       <c r="J6" t="n">
-        <v>47.55277358490567</v>
+        <v>47.71129057803813</v>
       </c>
       <c r="K6" t="n">
-        <v>81.27526415094341</v>
+        <v>81.54619494042197</v>
       </c>
       <c r="L6" t="n">
-        <v>109.2846226415094</v>
+        <v>109.6489225228995</v>
       </c>
       <c r="M6" t="n">
-        <v>127.53</v>
+        <v>127.9551207786668</v>
       </c>
       <c r="N6" t="n">
-        <v>130.9053396226415</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>119.7528113207547</v>
+        <v>120.1520068700076</v>
       </c>
       <c r="P6" t="n">
-        <v>96.11218867924529</v>
+        <v>96.43257830122204</v>
       </c>
       <c r="Q6" t="n">
-        <v>64.2484528301887</v>
+        <v>64.4626248077258</v>
       </c>
       <c r="R6" t="n">
-        <v>31.25003773584907</v>
+        <v>31.35420961992052</v>
       </c>
       <c r="S6" t="n">
-        <v>9.348962264150938</v>
+        <v>9.380126994939479</v>
       </c>
       <c r="T6" t="n">
-        <v>2.028735849056603</v>
+        <v>2.035498632431968</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03311320754716982</v>
+        <v>0.03322359030084825</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4219672131147539</v>
+        <v>0.423373839243596</v>
       </c>
       <c r="H7" t="n">
-        <v>3.751672131147543</v>
+        <v>3.764178316183975</v>
       </c>
       <c r="I7" t="n">
-        <v>12.68970491803279</v>
+        <v>12.73200600198015</v>
       </c>
       <c r="J7" t="n">
-        <v>29.83308196721311</v>
+        <v>29.93253043452224</v>
       </c>
       <c r="K7" t="n">
-        <v>49.02491803278687</v>
+        <v>49.18834241393778</v>
       </c>
       <c r="L7" t="n">
-        <v>62.73501639344263</v>
+        <v>62.94414333627064</v>
       </c>
       <c r="M7" t="n">
-        <v>66.14527868852458</v>
+        <v>66.36577372797568</v>
       </c>
       <c r="N7" t="n">
-        <v>64.57249180327874</v>
+        <v>64.78774396352233</v>
       </c>
       <c r="O7" t="n">
-        <v>59.64314754098363</v>
+        <v>59.84196775054031</v>
       </c>
       <c r="P7" t="n">
-        <v>51.0350163934426</v>
+        <v>51.20514142997091</v>
       </c>
       <c r="Q7" t="n">
-        <v>35.334</v>
+        <v>35.45178575702513</v>
       </c>
       <c r="R7" t="n">
-        <v>18.97318032786885</v>
+        <v>19.03642735362569</v>
       </c>
       <c r="S7" t="n">
-        <v>7.35373770491803</v>
+        <v>7.378251362090667</v>
       </c>
       <c r="T7" t="n">
-        <v>1.80295081967213</v>
+        <v>1.808960949495364</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02301639344262297</v>
+        <v>0.02309311850419617</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.045226130653265</v>
+        <v>1.048427708612923</v>
       </c>
       <c r="H8" t="n">
-        <v>10.70442211055275</v>
+        <v>10.7372102708321</v>
       </c>
       <c r="I8" t="n">
-        <v>40.29608040201003</v>
+        <v>40.41950923629976</v>
       </c>
       <c r="J8" t="n">
-        <v>88.71226130653262</v>
+        <v>88.98399123388617</v>
       </c>
       <c r="K8" t="n">
-        <v>132.9566834170853</v>
+        <v>133.3639361394712</v>
       </c>
       <c r="L8" t="n">
-        <v>164.9445226130652</v>
+        <v>165.449755626934</v>
       </c>
       <c r="M8" t="n">
-        <v>183.5325628140702</v>
+        <v>184.0947318899791</v>
       </c>
       <c r="N8" t="n">
-        <v>186.5023115577888</v>
+        <v>187.0735771170756</v>
       </c>
       <c r="O8" t="n">
-        <v>176.1088442211054</v>
+        <v>176.6482740895558</v>
       </c>
       <c r="P8" t="n">
-        <v>150.3048241206029</v>
+        <v>150.7652150331742</v>
       </c>
       <c r="Q8" t="n">
-        <v>112.8726633165828</v>
+        <v>113.2183977184739</v>
       </c>
       <c r="R8" t="n">
-        <v>65.65718592964821</v>
+        <v>65.8582970511566</v>
       </c>
       <c r="S8" t="n">
-        <v>23.81809045226131</v>
+        <v>23.89104641001701</v>
       </c>
       <c r="T8" t="n">
-        <v>4.575477386934671</v>
+        <v>4.589492294453073</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08361809045226121</v>
+        <v>0.08387421668903385</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5592452830188678</v>
+        <v>0.560958278245113</v>
       </c>
       <c r="H9" t="n">
-        <v>5.401132075471698</v>
+        <v>5.417676003051488</v>
       </c>
       <c r="I9" t="n">
-        <v>19.25471698113207</v>
+        <v>19.31369510624622</v>
       </c>
       <c r="J9" t="n">
-        <v>52.8364150943396</v>
+        <v>52.99825557753501</v>
       </c>
       <c r="K9" t="n">
-        <v>90.30584905660372</v>
+        <v>90.58246021995758</v>
       </c>
       <c r="L9" t="n">
-        <v>121.427358490566</v>
+        <v>121.799296335633</v>
       </c>
       <c r="M9" t="n">
-        <v>141.6999999999999</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>133.0586792452829</v>
+        <v>133.4662443858011</v>
       </c>
       <c r="P9" t="n">
-        <v>106.7913207547169</v>
+        <v>107.1184277115602</v>
       </c>
       <c r="Q9" t="n">
-        <v>71.38716981132072</v>
+        <v>71.60583214932356</v>
       </c>
       <c r="R9" t="n">
-        <v>34.72226415094339</v>
+        <v>34.82862011770975</v>
       </c>
       <c r="S9" t="n">
-        <v>10.38773584905659</v>
+        <v>10.41955398407041</v>
       </c>
       <c r="T9" t="n">
-        <v>2.254150943396225</v>
+        <v>2.261055516259907</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03679245283018869</v>
+        <v>0.03690514988454693</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4688524590163933</v>
+        <v>0.4702885766708382</v>
       </c>
       <c r="H10" t="n">
-        <v>4.168524590163936</v>
+        <v>4.181292981673455</v>
       </c>
       <c r="I10" t="n">
-        <v>14.09967213114754</v>
+        <v>14.14286010570121</v>
       </c>
       <c r="J10" t="n">
-        <v>33.147868852459</v>
+        <v>33.24940237062826</v>
       </c>
       <c r="K10" t="n">
-        <v>54.47213114754093</v>
+        <v>54.63898190775737</v>
       </c>
       <c r="L10" t="n">
-        <v>69.70557377049177</v>
+        <v>69.91908529886263</v>
       </c>
       <c r="M10" t="n">
-        <v>73.49475409836059</v>
+        <v>73.71987206850237</v>
       </c>
       <c r="N10" t="n">
-        <v>71.74721311475409</v>
+        <v>71.96697828272931</v>
       </c>
       <c r="O10" t="n">
-        <v>66.27016393442621</v>
+        <v>66.47315263707451</v>
       </c>
       <c r="P10" t="n">
-        <v>56.70557377049174</v>
+        <v>56.87926567298936</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.25999999999998</v>
+        <v>39.38025527013719</v>
       </c>
       <c r="R10" t="n">
-        <v>21.08131147540982</v>
+        <v>21.14588454739968</v>
       </c>
       <c r="S10" t="n">
-        <v>8.170819672131142</v>
+        <v>8.195847286163604</v>
       </c>
       <c r="T10" t="n">
-        <v>2.003278688524589</v>
+        <v>2.009414827593581</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02557377049180331</v>
+        <v>0.02565210418204575</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H11" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I11" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J11" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K11" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L11" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M11" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N11" t="n">
-        <v>229.4130635965929</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P11" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q11" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R11" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S11" t="n">
-        <v>29.31457286432163</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T11" t="n">
-        <v>5.631356783919597</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,19 +31749,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6883018867924527</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H12" t="n">
-        <v>6.647547169811323</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I12" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J12" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K12" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
@@ -31776,22 +31776,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.86113207547173</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R12" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S12" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T12" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5770491803278687</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H13" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I13" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J13" t="n">
-        <v>40.79737704918033</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K13" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L13" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M13" t="n">
-        <v>90.45508196721312</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N13" t="n">
-        <v>88.30426229508204</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O13" t="n">
-        <v>81.56327868852463</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P13" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R13" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S13" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T13" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H14" t="n">
-        <v>13.17467336683417</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I14" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J14" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K14" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L14" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M14" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>216.7493467336683</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P14" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q14" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R14" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S14" t="n">
-        <v>29.31457286432163</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T14" t="n">
-        <v>5.631356783919597</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,19 +31986,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6883018867924527</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H15" t="n">
-        <v>6.647547169811323</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I15" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J15" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K15" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L15" t="n">
         <v>138.5543797798742</v>
@@ -32013,22 +32013,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q15" t="n">
-        <v>87.86113207547173</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R15" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S15" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T15" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5770491803278687</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H16" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I16" t="n">
-        <v>17.35344262295083</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J16" t="n">
-        <v>40.79737704918033</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K16" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L16" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M16" t="n">
-        <v>90.45508196721312</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N16" t="n">
-        <v>88.30426229508204</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O16" t="n">
-        <v>81.56327868852463</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P16" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q16" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R16" t="n">
-        <v>25.94622950819672</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S16" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T16" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H17" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I17" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J17" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K17" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L17" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M17" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N17" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P17" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q17" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R17" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S17" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T17" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,19 +32223,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H18" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I18" t="n">
-        <v>23.69811320754718</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J18" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K18" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
@@ -32250,22 +32250,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q18" t="n">
-        <v>87.86113207547173</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R18" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S18" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T18" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H19" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I19" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J19" t="n">
-        <v>40.79737704918033</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K19" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L19" t="n">
-        <v>85.7914754098361</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M19" t="n">
-        <v>90.45508196721312</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N19" t="n">
-        <v>88.30426229508204</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O19" t="n">
-        <v>81.56327868852463</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P19" t="n">
-        <v>69.79147540983602</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.32000000000001</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R19" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S19" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T19" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H20" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I20" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J20" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K20" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L20" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M20" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N20" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P20" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q20" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R20" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S20" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T20" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,19 +32460,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H21" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I21" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J21" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K21" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -32487,22 +32487,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q21" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R21" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S21" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T21" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H22" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I22" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J22" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K22" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L22" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M22" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N22" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O22" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P22" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q22" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R22" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S22" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T22" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H23" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I23" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J23" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K23" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L23" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M23" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N23" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P23" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q23" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R23" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S23" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T23" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,19 +32697,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H24" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I24" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J24" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K24" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -32724,22 +32724,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q24" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R24" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S24" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T24" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U24" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H25" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I25" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J25" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K25" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L25" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M25" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N25" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O25" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P25" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q25" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R25" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S25" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T25" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U25" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H26" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I26" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J26" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K26" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L26" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M26" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N26" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P26" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q26" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R26" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S26" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T26" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,19 +32934,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H27" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I27" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J27" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K27" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L27" t="n">
         <v>138.5543797798742</v>
@@ -32961,22 +32961,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q27" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R27" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S27" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T27" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H28" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I28" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J28" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K28" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L28" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M28" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N28" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O28" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P28" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R28" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S28" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T28" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U28" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H29" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I29" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J29" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K29" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L29" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M29" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N29" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P29" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q29" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R29" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S29" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T29" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,19 +33171,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H30" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I30" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J30" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K30" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L30" t="n">
         <v>138.5543797798742</v>
@@ -33198,22 +33198,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q30" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R30" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S30" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T30" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H31" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I31" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J31" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K31" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L31" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M31" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N31" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O31" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P31" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q31" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R31" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S31" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T31" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U31" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H32" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I32" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179212</v>
       </c>
       <c r="J32" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K32" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L32" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718788</v>
       </c>
       <c r="M32" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N32" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P32" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q32" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R32" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S32" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T32" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,19 +33408,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014502</v>
       </c>
       <c r="H33" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100848</v>
       </c>
       <c r="I33" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J33" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K33" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
@@ -33435,22 +33435,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261111</v>
       </c>
       <c r="Q33" t="n">
-        <v>87.86113207547172</v>
+        <v>87.8120447468588</v>
       </c>
       <c r="R33" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602163</v>
       </c>
       <c r="S33" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T33" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U33" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877963</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554866</v>
       </c>
       <c r="H34" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I34" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J34" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K34" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073742</v>
       </c>
       <c r="L34" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224572</v>
       </c>
       <c r="M34" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904504</v>
       </c>
       <c r="N34" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307465</v>
       </c>
       <c r="O34" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P34" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q34" t="n">
-        <v>48.32</v>
+        <v>48.29300399320443</v>
       </c>
       <c r="R34" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S34" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T34" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U34" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H35" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I35" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J35" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K35" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L35" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M35" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N35" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P35" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q35" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R35" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S35" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T35" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,19 +33645,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H36" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I36" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J36" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K36" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
@@ -33672,22 +33672,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q36" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R36" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S36" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T36" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H37" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I37" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J37" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K37" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L37" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M37" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N37" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O37" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P37" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R37" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S37" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T37" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U37" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H38" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I38" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J38" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K38" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L38" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M38" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N38" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P38" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q38" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R38" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S38" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T38" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,19 +33882,19 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H39" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I39" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J39" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K39" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L39" t="n">
         <v>138.5543797798742</v>
@@ -33909,22 +33909,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q39" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R39" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S39" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T39" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U39" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H40" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I40" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J40" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K40" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L40" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M40" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N40" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O40" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P40" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q40" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R40" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S40" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T40" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U40" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H41" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I41" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J41" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K41" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L41" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M41" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N41" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P41" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q41" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R41" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S41" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T41" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,19 +34119,19 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H42" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I42" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J42" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K42" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
@@ -34146,22 +34146,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q42" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R42" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S42" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T42" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U42" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H43" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I43" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J43" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K43" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L43" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M43" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N43" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O43" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P43" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q43" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R43" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S43" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T43" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U43" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.286432160804019</v>
+        <v>1.28571344119816</v>
       </c>
       <c r="H44" t="n">
-        <v>13.17467336683416</v>
+        <v>13.16731277967066</v>
       </c>
       <c r="I44" t="n">
-        <v>49.595175879397</v>
+        <v>49.56746744179213</v>
       </c>
       <c r="J44" t="n">
-        <v>109.1843216080402</v>
+        <v>109.1233211798925</v>
       </c>
       <c r="K44" t="n">
-        <v>163.6389949748744</v>
+        <v>163.5475711458106</v>
       </c>
       <c r="L44" t="n">
-        <v>203.0086432160804</v>
+        <v>202.8952238718789</v>
       </c>
       <c r="M44" t="n">
-        <v>225.8862311557789</v>
+        <v>225.7600302817866</v>
       </c>
       <c r="N44" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>216.7493467336684</v>
+        <v>216.6282505656767</v>
       </c>
       <c r="P44" t="n">
-        <v>184.9905527638191</v>
+        <v>184.8871999860971</v>
       </c>
       <c r="Q44" t="n">
-        <v>138.9202010050251</v>
+        <v>138.8425873731879</v>
       </c>
       <c r="R44" t="n">
-        <v>80.80884422110555</v>
+        <v>80.76369695066401</v>
       </c>
       <c r="S44" t="n">
-        <v>29.31457286432162</v>
+        <v>29.29819504130311</v>
       </c>
       <c r="T44" t="n">
-        <v>5.631356783919596</v>
+        <v>5.62821058884495</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1029145728643215</v>
+        <v>0.1028570752958528</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,19 +34356,19 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6883018867924529</v>
+        <v>0.6879173379014503</v>
       </c>
       <c r="H45" t="n">
-        <v>6.647547169811322</v>
+        <v>6.643833237100849</v>
       </c>
       <c r="I45" t="n">
-        <v>23.69811320754717</v>
+        <v>23.68487325669467</v>
       </c>
       <c r="J45" t="n">
-        <v>65.02943396226416</v>
+        <v>64.99310252515413</v>
       </c>
       <c r="K45" t="n">
-        <v>111.1456603773585</v>
+        <v>111.0835641645513</v>
       </c>
       <c r="L45" t="n">
         <v>138.5543797798742</v>
@@ -34383,22 +34383,22 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>131.4354716981132</v>
+        <v>131.3620397261112</v>
       </c>
       <c r="Q45" t="n">
-        <v>87.86113207547172</v>
+        <v>87.81204474685882</v>
       </c>
       <c r="R45" t="n">
-        <v>42.73509433962266</v>
+        <v>42.71121857602164</v>
       </c>
       <c r="S45" t="n">
-        <v>12.78490566037735</v>
+        <v>12.77776283338877</v>
       </c>
       <c r="T45" t="n">
-        <v>2.774339622641508</v>
+        <v>2.772789620751897</v>
       </c>
       <c r="U45" t="n">
-        <v>0.04528301886792455</v>
+        <v>0.04525771959877964</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5770491803278688</v>
+        <v>0.5767267874554867</v>
       </c>
       <c r="H46" t="n">
-        <v>5.130491803278692</v>
+        <v>5.127625437558785</v>
       </c>
       <c r="I46" t="n">
-        <v>17.35344262295082</v>
+        <v>17.343747390025</v>
       </c>
       <c r="J46" t="n">
-        <v>40.79737704918032</v>
+        <v>40.77458387310291</v>
       </c>
       <c r="K46" t="n">
-        <v>67.04262295081965</v>
+        <v>67.00516676073744</v>
       </c>
       <c r="L46" t="n">
-        <v>85.79147540983607</v>
+        <v>85.74354438224573</v>
       </c>
       <c r="M46" t="n">
-        <v>90.45508196721309</v>
+        <v>90.40454541904505</v>
       </c>
       <c r="N46" t="n">
-        <v>88.30426229508203</v>
+        <v>88.25492739307467</v>
       </c>
       <c r="O46" t="n">
-        <v>81.56327868852462</v>
+        <v>81.51770992143554</v>
       </c>
       <c r="P46" t="n">
-        <v>69.79147540983604</v>
+        <v>69.75248345734356</v>
       </c>
       <c r="Q46" t="n">
-        <v>48.32</v>
+        <v>48.29300399320444</v>
       </c>
       <c r="R46" t="n">
-        <v>25.94622950819671</v>
+        <v>25.93173355231669</v>
       </c>
       <c r="S46" t="n">
-        <v>10.05639344262295</v>
+        <v>10.05077501411061</v>
       </c>
       <c r="T46" t="n">
-        <v>2.465573770491802</v>
+        <v>2.464196273673442</v>
       </c>
       <c r="U46" t="n">
-        <v>0.03147540983606561</v>
+        <v>0.03145782477029931</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
